--- a/src/main/python/책데이터-완-.csv.xlsx
+++ b/src/main/python/책데이터-완-.csv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2fbb8d8a723fddd8/바탕 화면/독서속도분석/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="8_{182E18F3-7789-4EB8-B058-B6AB69A1AE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{852D0DAB-853A-42EC-A9DB-13CBAD052AFF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6E7B3-0040-4181-AFB6-A4531EACA150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{10234875-0202-4C62-84D1-99BF638A4C97}"/>
+    <workbookView xWindow="45" yWindow="120" windowWidth="28800" windowHeight="13695" xr2:uid="{10234875-0202-4C62-84D1-99BF638A4C97}"/>
   </bookViews>
   <sheets>
     <sheet name="final_sampled_library_books (2)" sheetId="1" r:id="rId1"/>
@@ -56,1003 +56,1032 @@
     <t>박솔뫼 지음</t>
   </si>
   <si>
+    <t>박미연 지음</t>
+  </si>
+  <si>
+    <t>플나나 농장의 휴식</t>
+  </si>
+  <si>
+    <t>선자은 지음</t>
+  </si>
+  <si>
+    <t>은의 세계 :위수정 소설</t>
+  </si>
+  <si>
+    <t>위수정 지음</t>
+  </si>
+  <si>
+    <t>김지연 지음</t>
+  </si>
+  <si>
+    <t>케이크 손</t>
+  </si>
+  <si>
+    <t>단요 지음</t>
+  </si>
+  <si>
+    <t>있을 법한 모든 것</t>
+  </si>
+  <si>
+    <t>구병모 지음</t>
+  </si>
+  <si>
+    <t>스파클</t>
+  </si>
+  <si>
+    <t>최현진 지음</t>
+  </si>
+  <si>
+    <t>이기호 지음</t>
+  </si>
+  <si>
+    <t>박서련 지음</t>
+  </si>
+  <si>
+    <t>클로버:나혜림 장편소설</t>
+  </si>
+  <si>
+    <t>나혜림 지음</t>
+  </si>
+  <si>
+    <t>전건우 지음</t>
+  </si>
+  <si>
+    <t>이유리 지음</t>
+  </si>
+  <si>
+    <t>젊은작가상 수상작품집</t>
+  </si>
+  <si>
+    <t>김멜라...외[등]지음</t>
+  </si>
+  <si>
+    <t>고정욱 지음</t>
+  </si>
+  <si>
+    <t>비트코인 삼국지</t>
+  </si>
+  <si>
+    <t>박촌 이영춘 지음</t>
+  </si>
+  <si>
+    <t>불편한 편의점:큰글씨책</t>
+  </si>
+  <si>
+    <t>김호연 지음</t>
+  </si>
+  <si>
+    <t>김보영</t>
+  </si>
+  <si>
+    <t>우리에게 남은 시간 46일</t>
+  </si>
+  <si>
+    <t>이설 지음</t>
+  </si>
+  <si>
+    <t>촉법소년 살인 사건</t>
+  </si>
+  <si>
+    <t>송하강의 비정</t>
+  </si>
+  <si>
+    <t>백동수 지음</t>
+  </si>
+  <si>
+    <t>근접한 세계</t>
+  </si>
+  <si>
+    <t>김연수;히라노 게이치로 [공]지음;최고은 옮김</t>
+  </si>
+  <si>
+    <t>시간 도둑</t>
+  </si>
+  <si>
+    <t>손더 지음</t>
+  </si>
+  <si>
+    <t>비가 오면 열리는 상점=The rainbow goblin store:유영광 장편소설</t>
+  </si>
+  <si>
+    <t>유영광 지음</t>
+  </si>
+  <si>
+    <t>마이카시대</t>
+  </si>
+  <si>
+    <t>스토리공장,김한수 [공]지음</t>
+  </si>
+  <si>
+    <t>객석</t>
+  </si>
+  <si>
+    <t>양정숙</t>
+  </si>
+  <si>
+    <t>조금 망한 사랑</t>
+  </si>
+  <si>
+    <t>함윤이 지음</t>
+  </si>
+  <si>
+    <t>끼리끼리 사이언스</t>
+  </si>
+  <si>
+    <t>권혜영 [외]지음</t>
+  </si>
+  <si>
+    <t>노랜드:천선란 소설집</t>
+  </si>
+  <si>
+    <t>천선란</t>
+  </si>
+  <si>
+    <t>푸른 살=Blue flesh:이태제 장편소설</t>
+  </si>
+  <si>
+    <t>이태제 지음</t>
+  </si>
+  <si>
+    <t>정생, 꿈 밖은 위험해!</t>
+  </si>
+  <si>
+    <t>이문영 지음</t>
+  </si>
+  <si>
+    <t>산책하기 좋은 날</t>
+  </si>
+  <si>
+    <t>오한기 지음</t>
+  </si>
+  <si>
+    <t>민트 돔 아래에서:송가을 정치부 가다</t>
+  </si>
+  <si>
+    <t>송경화 지음</t>
+  </si>
+  <si>
+    <t>삼개주막 기담회.</t>
+  </si>
+  <si>
+    <t>오윤희 지음</t>
+  </si>
+  <si>
+    <t>바늘과 가죽의 시(詩)</t>
+  </si>
+  <si>
+    <t>설탕 실</t>
+  </si>
+  <si>
+    <t>연소민 지음</t>
+  </si>
+  <si>
+    <t>스노볼 드라이브</t>
+  </si>
+  <si>
+    <t>조예은 지음</t>
+  </si>
+  <si>
+    <t>마주:최은미 장편소설</t>
+  </si>
+  <si>
+    <t>최은미 지음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">삼개주막 기담회 :오윤희 기담소설 </t>
+  </si>
+  <si>
+    <t>치유의 빛</t>
+  </si>
+  <si>
+    <t>강화길 지음</t>
+  </si>
+  <si>
+    <t>나쁜 교육</t>
+  </si>
+  <si>
+    <t>김응수 지음;이준용 그림</t>
+  </si>
+  <si>
+    <t>정대건 지음</t>
+  </si>
+  <si>
+    <t>김선영 지음</t>
+  </si>
+  <si>
+    <t>광인</t>
+  </si>
+  <si>
+    <t>이혁진 지음</t>
+  </si>
+  <si>
+    <t>부천국제판타스틱영화제</t>
+  </si>
+  <si>
+    <t>너의 유토피아</t>
+  </si>
+  <si>
+    <t>정보라 지음</t>
+  </si>
+  <si>
+    <t>어느 노동자의 모험</t>
+  </si>
+  <si>
+    <t>배명은...외[등]지음</t>
+  </si>
+  <si>
+    <t>나태주 지음</t>
+  </si>
+  <si>
+    <t>장강명 지음</t>
+  </si>
+  <si>
+    <t>(남인숙의) 어른수업</t>
+  </si>
+  <si>
+    <t>남인숙 지음</t>
+  </si>
+  <si>
+    <t>아버지의 섬 낮달</t>
+  </si>
+  <si>
+    <t>안숙 지음</t>
+  </si>
+  <si>
+    <t>열심히 대충 쓰는 사람</t>
+  </si>
+  <si>
+    <t>윤덕원 지음</t>
+  </si>
+  <si>
+    <t>행복한 사람</t>
+  </si>
+  <si>
+    <t>나태주 지음;이경국 그림</t>
+  </si>
+  <si>
+    <t>좋아하기 때문에</t>
+  </si>
+  <si>
+    <t>김초엽 지음</t>
+  </si>
+  <si>
+    <t>빛과 실</t>
+  </si>
+  <si>
+    <t>한강 지음</t>
+  </si>
+  <si>
+    <t>쇳밥일지</t>
+  </si>
+  <si>
+    <t>천현우 지음</t>
+  </si>
+  <si>
+    <t>절대! 허송세월하지 마라</t>
+  </si>
+  <si>
+    <t>백낙원 지음</t>
+  </si>
+  <si>
+    <t>마시지 않을 수 없는 밤이니까요</t>
+  </si>
+  <si>
+    <t>정지아 지음</t>
+  </si>
+  <si>
+    <t>벼랑 끝이지만 아직 떨어지진 않았어</t>
+  </si>
+  <si>
+    <t>소재원 지음</t>
+  </si>
+  <si>
+    <t>무정형의 삶</t>
+  </si>
+  <si>
+    <t>김민철 지음</t>
+  </si>
+  <si>
+    <t>해방의 밤</t>
+  </si>
+  <si>
+    <t>은유 지음</t>
+  </si>
+  <si>
+    <t>나는 세계와 맞지 않지만</t>
+  </si>
+  <si>
+    <t>진은영 지음</t>
+  </si>
+  <si>
+    <t>즐거운 어른:이옥선 산문</t>
+  </si>
+  <si>
+    <t>이옥선 지음</t>
+  </si>
+  <si>
+    <t>꼭대기의 수줍음</t>
+  </si>
+  <si>
+    <t>유계영 지음</t>
+  </si>
+  <si>
+    <t>책 읽는 책 쓰는 책 만드는</t>
+  </si>
+  <si>
+    <t>이하영 지음</t>
+  </si>
+  <si>
+    <t>또 못 버린 물건들</t>
+  </si>
+  <si>
+    <t>은희경 지음</t>
+  </si>
+  <si>
+    <t>미스 에세이</t>
+  </si>
+  <si>
+    <t>김정화 지음</t>
+  </si>
+  <si>
+    <t>유형준 [외]지음</t>
+  </si>
+  <si>
+    <t>현인숙 글, 박혜정 그림</t>
+  </si>
+  <si>
+    <t>영화 보고 오는 길에 글을 썼습니다</t>
+  </si>
+  <si>
+    <t>김중혁 지음</t>
+  </si>
+  <si>
+    <t>사실, 내성적인 사람입니다:남인숙 공감 에세이</t>
+  </si>
+  <si>
+    <t>임봉근;임다운 [공]지음</t>
+  </si>
+  <si>
+    <t>정용준 지음</t>
+  </si>
+  <si>
+    <t>보편의 단어</t>
+  </si>
+  <si>
+    <t>이기주 지음</t>
+  </si>
+  <si>
+    <t>신명진 지음</t>
+  </si>
+  <si>
+    <t>이에니 지음</t>
+  </si>
+  <si>
+    <t>고선경 지음</t>
+  </si>
+  <si>
+    <t>강보원 지음</t>
+  </si>
+  <si>
+    <t>권여선 지음</t>
+  </si>
+  <si>
+    <t>하재영 지음</t>
+  </si>
+  <si>
+    <t>조우성 지음</t>
+  </si>
+  <si>
+    <t>오은 지음</t>
+  </si>
+  <si>
+    <t>산을 등에 지고 가려 했네</t>
+  </si>
+  <si>
+    <t>손봉호 지음</t>
+  </si>
+  <si>
+    <t>내 서랍 속 작은 사치</t>
+  </si>
+  <si>
+    <t>이지수 지음</t>
+  </si>
+  <si>
+    <t>전소영 지음</t>
+  </si>
+  <si>
+    <t>임경선 지음</t>
+  </si>
+  <si>
+    <t>우리는 영영 볼 수 없겠지만</t>
+  </si>
+  <si>
+    <t>도티끌 지음</t>
+  </si>
+  <si>
+    <t>일단 떠나는 수밖에</t>
+  </si>
+  <si>
+    <t>김남희 지음</t>
+  </si>
+  <si>
+    <t>마산에서 아프리카까지</t>
+  </si>
+  <si>
+    <t>박지윤 지음</t>
+  </si>
+  <si>
+    <t>김병종의 화첩기행</t>
+  </si>
+  <si>
+    <t>김병종 지음</t>
+  </si>
+  <si>
+    <t>나랑 같이 여행 갈래</t>
+  </si>
+  <si>
+    <t>송도아 저</t>
+  </si>
+  <si>
+    <t>민혜</t>
+  </si>
+  <si>
+    <t>이오덕;권정생 [공]지음</t>
+  </si>
+  <si>
+    <t>느림과 기다림의 장항선 인문학 기행</t>
+  </si>
+  <si>
+    <t>이심훈 지음</t>
+  </si>
+  <si>
+    <t>마음속에 바람이 생기자 운명의 바람이 불었다</t>
+  </si>
+  <si>
+    <t>김동조 지음</t>
+  </si>
+  <si>
+    <t>완전 (망)한 여행</t>
+  </si>
+  <si>
+    <t>허휘수,서솔 [공]지음</t>
+  </si>
+  <si>
+    <t>장르</t>
+  </si>
+  <si>
+    <t>우리 세희</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>조해진 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167903594</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수필</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788963721606</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193811252</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>손원평 지음</t>
+  </si>
+  <si>
+    <t>9788936411725</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>세계 괴담모음 2022</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791158965341</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>착한 거짓말이 물어다 준 행복</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소설</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근 1년간 대출건수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788983949615</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954684682</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788936457136</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954638746</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791168343870</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198173898</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198159601</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791194087755</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791171712304</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791191859591</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791172131265</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791189784423</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>기록문학</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>어머니의 불:53년 엄마의 일기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791196074456</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954452342</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954685436</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167902412</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954694179</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788936457341</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791141602468</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791168343764</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937428234</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198042934</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791161571331</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193282151</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791190749787</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788994938585</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791170613596</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791194293545</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198757050</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791191938173</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791141601508</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791141615208</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791194643692</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791160408317</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791170610106</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791192988290</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167900920</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791160405156</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791163166320</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791190885713</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791191824520</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937473319</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788936439286</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791163162322</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167375629</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791197790911</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937473401</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167031952</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937454677</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791197522130</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791168342569</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193367025</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193153710</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198569608</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791155552261</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791189782726</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788934956938</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791170401421</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788932043562</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788954688109</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791162845226</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193289037</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788936480103</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791194184058</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788998690779</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791159333316</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791197332678</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788960908949</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937419454</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791188083183</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791192638461</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788950980771</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791192638843</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791160263558</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791195522170</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791173351631</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791158162054</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791124065037</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788937449291</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791141602581</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791165345112</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791171714599</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167552815</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791155251744</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791191592337</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198886101</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791196553876</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791193238677</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9788958720089</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791198737878</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791156344605</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791197646904</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791196895099</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791167822048</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>9791141610869</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>두 번째 달에게</t>
-  </si>
-  <si>
-    <t>박미연 지음</t>
-  </si>
-  <si>
-    <t>플나나 농장의 휴식</t>
-  </si>
-  <si>
-    <t>선자은 지음</t>
-  </si>
-  <si>
-    <t>은의 세계 :위수정 소설</t>
-  </si>
-  <si>
-    <t>위수정 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>명랑한 이시봉의 짧고 투쟁 없는 삶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>사랑의 힘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>마음에 없는 소리 :김지연 소설</t>
-  </si>
-  <si>
-    <t>김지연 지음</t>
-  </si>
-  <si>
-    <t>케이크 손</t>
-  </si>
-  <si>
-    <t>단요 지음</t>
-  </si>
-  <si>
-    <t>있을 법한 모든 것</t>
-  </si>
-  <si>
-    <t>구병모 지음</t>
-  </si>
-  <si>
-    <t>스파클</t>
-  </si>
-  <si>
-    <t>최현진 지음</t>
-  </si>
-  <si>
-    <t>명랑한 이시봉의 짧고 투쟁 없는 삶</t>
-  </si>
-  <si>
-    <t>이기호 지음</t>
-  </si>
-  <si>
-    <t>사랑의 힘</t>
-  </si>
-  <si>
-    <t>박서련 지음</t>
-  </si>
-  <si>
-    <t>클로버:나혜림 장편소설</t>
-  </si>
-  <si>
-    <t>나혜림 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>흉담</t>
-  </si>
-  <si>
-    <t>전건우 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>비눗방울 퐁</t>
-  </si>
-  <si>
-    <t>이유리 지음</t>
-  </si>
-  <si>
-    <t>젊은작가상 수상작품집</t>
-  </si>
-  <si>
-    <t>김멜라...외[등]지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>점퍼</t>
-  </si>
-  <si>
-    <t>고정욱 지음</t>
-  </si>
-  <si>
-    <t>비트코인 삼국지</t>
-  </si>
-  <si>
-    <t>박촌 이영춘 지음</t>
-  </si>
-  <si>
-    <t>불편한 편의점:큰글씨책</t>
-  </si>
-  <si>
-    <t>김호연 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>당신을 기다리고 있어</t>
-  </si>
-  <si>
-    <t>김보영</t>
-  </si>
-  <si>
-    <t>우리에게 남은 시간 46일</t>
-  </si>
-  <si>
-    <t>이설 지음</t>
-  </si>
-  <si>
-    <t>촉법소년 살인 사건</t>
-  </si>
-  <si>
-    <t>송하강의 비정</t>
-  </si>
-  <si>
-    <t>백동수 지음</t>
-  </si>
-  <si>
-    <t>근접한 세계</t>
-  </si>
-  <si>
-    <t>김연수;히라노 게이치로 [공]지음;최고은 옮김</t>
-  </si>
-  <si>
-    <t>시간 도둑</t>
-  </si>
-  <si>
-    <t>손더 지음</t>
-  </si>
-  <si>
-    <t>비가 오면 열리는 상점=The rainbow goblin store:유영광 장편소설</t>
-  </si>
-  <si>
-    <t>유영광 지음</t>
-  </si>
-  <si>
-    <t>마이카시대</t>
-  </si>
-  <si>
-    <t>스토리공장,김한수 [공]지음</t>
-  </si>
-  <si>
-    <t>객석</t>
-  </si>
-  <si>
-    <t>양정숙</t>
-  </si>
-  <si>
-    <t>조금 망한 사랑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>정전</t>
-  </si>
-  <si>
-    <t>함윤이 지음</t>
-  </si>
-  <si>
-    <t>끼리끼리 사이언스</t>
-  </si>
-  <si>
-    <t>권혜영 [외]지음</t>
-  </si>
-  <si>
-    <t>노랜드:천선란 소설집</t>
-  </si>
-  <si>
-    <t>천선란</t>
-  </si>
-  <si>
-    <t>푸른 살=Blue flesh:이태제 장편소설</t>
-  </si>
-  <si>
-    <t>이태제 지음</t>
-  </si>
-  <si>
-    <t>정생, 꿈 밖은 위험해!</t>
-  </si>
-  <si>
-    <t>이문영 지음</t>
-  </si>
-  <si>
-    <t>산책하기 좋은 날</t>
-  </si>
-  <si>
-    <t>오한기 지음</t>
-  </si>
-  <si>
-    <t>민트 돔 아래에서:송가을 정치부 가다</t>
-  </si>
-  <si>
-    <t>송경화 지음</t>
-  </si>
-  <si>
-    <t>삼개주막 기담회.</t>
-  </si>
-  <si>
-    <t>오윤희 지음</t>
-  </si>
-  <si>
-    <t>바늘과 가죽의 시(詩)</t>
-  </si>
-  <si>
-    <t>설탕 실</t>
-  </si>
-  <si>
-    <t>연소민 지음</t>
-  </si>
-  <si>
-    <t>스노볼 드라이브</t>
-  </si>
-  <si>
-    <t>조예은 지음</t>
-  </si>
-  <si>
-    <t>마주:최은미 장편소설</t>
-  </si>
-  <si>
-    <t>최은미 지음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">삼개주막 기담회 :오윤희 기담소설 </t>
-  </si>
-  <si>
-    <t>치유의 빛</t>
-  </si>
-  <si>
-    <t>강화길 지음</t>
-  </si>
-  <si>
-    <t>나쁜 교육</t>
-  </si>
-  <si>
-    <t>김응수 지음;이준용 그림</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>나쁜 의도는 없었습니다 : [큰글씨책]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>급류</t>
-  </si>
-  <si>
-    <t>정대건 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>내일은 내일에게</t>
-  </si>
-  <si>
-    <t>김선영 지음</t>
-  </si>
-  <si>
-    <t>광인</t>
-  </si>
-  <si>
-    <t>이혁진 지음</t>
-  </si>
-  <si>
-    <t>부천국제판타스틱영화제</t>
-  </si>
-  <si>
-    <t>너의 유토피아</t>
-  </si>
-  <si>
-    <t>정보라 지음</t>
-  </si>
-  <si>
-    <t>어느 노동자의 모험</t>
-  </si>
-  <si>
-    <t>배명은...외[등]지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>너를 아끼며 살아라</t>
-  </si>
-  <si>
-    <t>나태주 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>소설가라는 이상한 직업</t>
-  </si>
-  <si>
-    <t>장강명 지음</t>
-  </si>
-  <si>
-    <t>(남인숙의) 어른수업</t>
-  </si>
-  <si>
-    <t>남인숙 지음</t>
-  </si>
-  <si>
-    <t>아버지의 섬 낮달</t>
-  </si>
-  <si>
-    <t>안숙 지음</t>
-  </si>
-  <si>
-    <t>열심히 대충 쓰는 사람</t>
-  </si>
-  <si>
-    <t>윤덕원 지음</t>
-  </si>
-  <si>
-    <t>행복한 사람</t>
-  </si>
-  <si>
-    <t>나태주 지음;이경국 그림</t>
-  </si>
-  <si>
-    <t>좋아하기 때문에</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>책과 우연들</t>
-  </si>
-  <si>
-    <t>김초엽 지음</t>
-  </si>
-  <si>
-    <t>빛과 실</t>
-  </si>
-  <si>
-    <t>한강 지음</t>
-  </si>
-  <si>
-    <t>쇳밥일지</t>
-  </si>
-  <si>
-    <t>천현우 지음</t>
-  </si>
-  <si>
-    <t>절대! 허송세월하지 마라</t>
-  </si>
-  <si>
-    <t>백낙원 지음</t>
-  </si>
-  <si>
-    <t>마시지 않을 수 없는 밤이니까요</t>
-  </si>
-  <si>
-    <t>정지아 지음</t>
-  </si>
-  <si>
-    <t>벼랑 끝이지만 아직 떨어지진 않았어</t>
-  </si>
-  <si>
-    <t>소재원 지음</t>
-  </si>
-  <si>
-    <t>무정형의 삶</t>
-  </si>
-  <si>
-    <t>김민철 지음</t>
-  </si>
-  <si>
-    <t>해방의 밤</t>
-  </si>
-  <si>
-    <t>은유 지음</t>
-  </si>
-  <si>
-    <t>나는 세계와 맞지 않지만</t>
-  </si>
-  <si>
-    <t>진은영 지음</t>
-  </si>
-  <si>
-    <t>즐거운 어른:이옥선 산문</t>
-  </si>
-  <si>
-    <t>이옥선 지음</t>
-  </si>
-  <si>
-    <t>꼭대기의 수줍음</t>
-  </si>
-  <si>
-    <t>유계영 지음</t>
-  </si>
-  <si>
-    <t>책 읽는 책 쓰는 책 만드는</t>
-  </si>
-  <si>
-    <t>이하영 지음</t>
-  </si>
-  <si>
-    <t>또 못 버린 물건들</t>
-  </si>
-  <si>
-    <t>은희경 지음</t>
-  </si>
-  <si>
-    <t>미스 에세이</t>
-  </si>
-  <si>
-    <t>김정화 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘내일하는 사이</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>별을 위한 시간</t>
-  </si>
-  <si>
-    <t>유형준 [외]지음</t>
-  </si>
-  <si>
-    <t>현인숙 글, 박혜정 그림</t>
-  </si>
-  <si>
-    <t>영화 보고 오는 길에 글을 썼습니다</t>
-  </si>
-  <si>
-    <t>김중혁 지음</t>
-  </si>
-  <si>
-    <t>사실, 내성적인 사람입니다:남인숙 공감 에세이</t>
-  </si>
-  <si>
-    <t>오늘내일하는 사이</t>
-  </si>
-  <si>
-    <t>임봉근;임다운 [공]지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>밑줄과 생각</t>
-  </si>
-  <si>
-    <t>정용준 지음</t>
-  </si>
-  <si>
-    <t>보편의 단어</t>
-  </si>
-  <si>
-    <t>이기주 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>다리가 될게</t>
-  </si>
-  <si>
-    <t>신명진 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>쉽게 자주 반하는 마음</t>
-  </si>
-  <si>
-    <t>이에니 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>29.9세</t>
-  </si>
-  <si>
-    <t>고선경 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>지나가기 혹은 영원히 남아 있기</t>
-  </si>
-  <si>
-    <t>강보원 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>술꾼들의 모국어</t>
-  </si>
-  <si>
-    <t>권여선 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>지극히 나라는 통증</t>
-  </si>
-  <si>
-    <t>하재영 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>한 개의 기쁨이 천 개의 슬픔을 이긴다:조우성 변호사 에세이</t>
-  </si>
-  <si>
-    <t>조우성 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>밤에만 착해지는 사람들</t>
-  </si>
-  <si>
-    <t>오은 지음</t>
-  </si>
-  <si>
-    <t>산을 등에 지고 가려 했네</t>
-  </si>
-  <si>
-    <t>손봉호 지음</t>
-  </si>
-  <si>
-    <t>내 서랍 속 작은 사치</t>
-  </si>
-  <si>
-    <t>이지수 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>그리는 마음</t>
-  </si>
-  <si>
-    <t>전소영 지음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>태도에 관하여</t>
-  </si>
-  <si>
-    <t>임경선 지음</t>
-  </si>
-  <si>
-    <t>우리는 영영 볼 수 없겠지만</t>
-  </si>
-  <si>
-    <t>도티끌 지음</t>
-  </si>
-  <si>
-    <t>일단 떠나는 수밖에</t>
-  </si>
-  <si>
-    <t>김남희 지음</t>
-  </si>
-  <si>
-    <t>마산에서 아프리카까지</t>
-  </si>
-  <si>
-    <t>박지윤 지음</t>
-  </si>
-  <si>
-    <t>김병종의 화첩기행</t>
-  </si>
-  <si>
-    <t>김병종 지음</t>
-  </si>
-  <si>
-    <t>나랑 같이 여행 갈래</t>
-  </si>
-  <si>
-    <t>송도아 저</t>
-  </si>
-  <si>
-    <t>민혜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>아름다운 편지</t>
-  </si>
-  <si>
-    <t>이오덕;권정생 [공]지음</t>
-  </si>
-  <si>
-    <t>느림과 기다림의 장항선 인문학 기행</t>
-  </si>
-  <si>
-    <t>이심훈 지음</t>
-  </si>
-  <si>
-    <t>마음속에 바람이 생기자 운명의 바람이 불었다</t>
-  </si>
-  <si>
-    <t>김동조 지음</t>
-  </si>
-  <si>
-    <t>완전 (망)한 여행</t>
-  </si>
-  <si>
-    <t>허휘수,서솔 [공]지음</t>
-  </si>
-  <si>
-    <t>장르</t>
-  </si>
-  <si>
-    <t>우리 세희</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>조해진 지음</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167903594</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수필</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788963721606</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193811252</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>나쁜 의도는 없었습니다 : [큰글씨책]</t>
-  </si>
-  <si>
-    <t>손원평 지음</t>
-  </si>
-  <si>
-    <t>9788936411725</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>세계 괴담모음 2022</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791158965341</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>착한 거짓말이 물어다 준 행복</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>소설</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>최근 1년간 대출건수</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788983949615</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954684682</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788936457136</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954638746</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791168343870</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198173898</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198159601</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791194087755</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791171712304</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791191859591</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791172131265</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791189784423</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>기록문학</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>어머니의 불:53년 엄마의 일기</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791196074456</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954452342</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954685436</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167902412</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954694179</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788936457341</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791141602468</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791168343764</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937428234</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198042934</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791161571331</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193282151</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791190749787</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788994938585</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791170613596</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791194293545</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198757050</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791191938173</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791141601508</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791141615208</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791194643692</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791160408317</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791170610106</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791192988290</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167900920</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791160405156</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791163166320</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791190885713</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791191824520</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937473319</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788936439286</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791163162322</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167375629</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791197790911</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937473401</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167031952</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937454677</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791197522130</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791168342569</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193367025</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193153710</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198569608</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791155552261</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791189782726</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788934956938</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791170401421</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788932043562</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788954688109</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791162845226</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193289037</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788936480103</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791194184058</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788998690779</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791159333316</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791197332678</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788960908949</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937419454</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791188083183</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791192638461</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788950980771</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791192638843</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791160263558</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791195522170</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791173351631</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791158162054</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791124065037</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788937449291</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791141602581</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791165345112</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791171714599</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167552815</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791155251744</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791191592337</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198886101</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791196553876</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791193238677</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9788958720089</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791198737878</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791156344605</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791197646904</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791196895099</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791167822048</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>9791141610869</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1654,7 +1683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1665,9 +1694,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
@@ -1735,10 +1761,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2065,9 +2087,8 @@
     <col min="2" max="2" width="42.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2084,14 +2105,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2101,2366 +2122,2266 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>221</v>
+      <c r="C2" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="D2">
         <v>813.7</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1242</v>
+      </c>
+      <c r="H2" s="2">
         <v>66690</v>
       </c>
-      <c r="F2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G2" s="7">
-        <v>1242</v>
-      </c>
-      <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>222</v>
+      <c r="C3" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="D3">
         <v>813.7</v>
       </c>
-      <c r="E3">
-        <v>32000</v>
-      </c>
       <c r="F3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G3" s="7">
+        <v>176</v>
+      </c>
+      <c r="G3" s="6">
         <v>2640</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3">
+        <v>97400</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>207</v>
+      <c r="C4" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="D4">
         <v>813.7</v>
       </c>
-      <c r="E4" s="2">
-        <v>41250</v>
-      </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G4" s="3">
         <v>693</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="2">
+        <v>41250</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>208</v>
+      <c r="C5" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="D5">
         <v>813.7</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1778</v>
+      </c>
+      <c r="H5" s="2">
         <v>142500</v>
       </c>
-      <c r="F5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G5" s="7">
-        <v>1778</v>
-      </c>
-      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>278</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>223</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="D6">
         <v>813.7</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="6">
+        <v>15243</v>
+      </c>
+      <c r="H6" s="2">
         <v>127555</v>
       </c>
-      <c r="F6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G6" s="7">
-        <v>15243</v>
-      </c>
-      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>224</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="D7">
         <v>813.7</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1376</v>
+      </c>
+      <c r="H7" s="2">
         <v>78988</v>
       </c>
-      <c r="F7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1376</v>
-      </c>
-      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>225</v>
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="D8">
         <v>813.7</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="6">
+        <v>10385</v>
+      </c>
+      <c r="H8" s="2">
         <v>126430</v>
       </c>
-      <c r="F8" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" s="7">
-        <v>10385</v>
-      </c>
-      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>226</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="D9">
         <v>813.7</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="6">
+        <v>3974</v>
+      </c>
+      <c r="H9" s="2">
         <v>73480</v>
       </c>
-      <c r="F9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G9" s="7">
-        <v>3974</v>
-      </c>
-      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>303</v>
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="D10">
         <v>813.7</v>
       </c>
-      <c r="E10">
-        <v>72000</v>
-      </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G10" s="3">
         <v>444</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10">
+        <v>230200</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>227</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="D11">
         <v>813.7</v>
       </c>
-      <c r="E11">
-        <v>55000</v>
-      </c>
       <c r="F11" t="s">
-        <v>205</v>
-      </c>
-      <c r="H11" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H11">
+        <v>175000</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>209</v>
+        <v>22</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="D12">
         <v>813.7</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G12" s="6">
+        <v>16497</v>
+      </c>
+      <c r="H12" s="2">
         <v>82720</v>
       </c>
-      <c r="F12" t="s">
-        <v>205</v>
-      </c>
-      <c r="G12" s="7">
-        <v>16497</v>
-      </c>
-      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>228</v>
+        <v>23</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="D13">
         <v>813.7</v>
       </c>
-      <c r="E13" s="2">
-        <v>29000</v>
-      </c>
       <c r="F13" t="s">
-        <v>205</v>
-      </c>
-      <c r="H13" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H13" s="2">
+        <v>81600</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>280</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>229</v>
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="D14">
         <v>813.7</v>
       </c>
-      <c r="E14" s="2">
-        <v>41000</v>
-      </c>
       <c r="F14" t="s">
-        <v>205</v>
-      </c>
-      <c r="G14" s="7">
+        <v>176</v>
+      </c>
+      <c r="G14" s="6">
         <v>4822</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="2">
+        <v>122000</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>210</v>
+        <v>26</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="D15">
         <v>813.7</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="6">
+        <v>10897</v>
+      </c>
+      <c r="H15" s="2">
         <v>163660</v>
       </c>
-      <c r="F15" t="s">
-        <v>205</v>
-      </c>
-      <c r="G15" s="7">
-        <v>10897</v>
-      </c>
-      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>281</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>198</v>
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="D16">
         <v>813.7</v>
       </c>
-      <c r="E16" s="2">
-        <v>22000</v>
-      </c>
       <c r="F16" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" s="7">
+        <v>176</v>
+      </c>
+      <c r="G16" s="6">
         <v>2923</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="2">
+        <v>63000</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>230</v>
+        <v>29</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="D17">
         <v>813.7</v>
       </c>
-      <c r="E17" s="2">
-        <v>90404</v>
-      </c>
       <c r="F17" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G17" s="3">
         <v>35</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="2">
+        <v>90404</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>231</v>
+        <v>31</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="D18">
         <v>813.7</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G18" s="6">
+        <v>14349</v>
+      </c>
+      <c r="H18" s="2">
         <v>110290</v>
       </c>
-      <c r="F18" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="7">
-        <v>14349</v>
-      </c>
-      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>195</v>
+        <v>166</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="D19">
         <v>813.7</v>
       </c>
-      <c r="E19" s="2">
-        <v>56000</v>
-      </c>
       <c r="F19" t="s">
-        <v>205</v>
-      </c>
-      <c r="H19" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H19" s="2">
+        <v>54400</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>211</v>
+        <v>32</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="D20">
         <v>813.7</v>
       </c>
-      <c r="E20" s="2">
-        <v>40000</v>
-      </c>
       <c r="F20" t="s">
-        <v>205</v>
-      </c>
-      <c r="H20" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H20" s="2">
+        <v>118000</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>232</v>
+        <v>34</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="D21">
         <v>813.7</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="6">
+        <v>3228</v>
+      </c>
+      <c r="H21" s="2">
         <v>58956</v>
       </c>
-      <c r="F21" t="s">
-        <v>205</v>
-      </c>
-      <c r="G21" s="7">
-        <v>3228</v>
-      </c>
-      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>233</v>
+        <v>23</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="D22">
         <v>813.7</v>
       </c>
-      <c r="E22" s="2">
-        <v>70416</v>
-      </c>
       <c r="F22" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G22" s="3">
         <v>864</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="2">
+        <v>70416</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>234</v>
+        <v>37</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="D23">
         <v>813.7</v>
       </c>
-      <c r="E23" s="2">
-        <v>117764</v>
-      </c>
       <c r="F23" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G23" s="3">
         <v>12</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="2">
+        <v>117764</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>235</v>
+        <v>39</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="D24">
         <v>813.7</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="2">
         <v>73144</v>
       </c>
-      <c r="F24" t="s">
-        <v>205</v>
-      </c>
-      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>236</v>
+        <v>41</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="D25">
         <v>813.7</v>
       </c>
-      <c r="E25" s="2">
-        <v>117754</v>
-      </c>
       <c r="F25" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G25" s="3">
         <v>296</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="2">
+        <v>117754</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>212</v>
+        <v>43</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="D26">
         <v>813.7</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" s="6">
+        <v>33367</v>
+      </c>
+      <c r="H26" s="2">
         <v>119087</v>
       </c>
-      <c r="F26" t="s">
-        <v>205</v>
-      </c>
-      <c r="G26" s="7">
-        <v>33367</v>
-      </c>
-      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>237</v>
+        <v>45</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="D27">
         <v>813.7</v>
       </c>
-      <c r="E27" s="2">
-        <v>87560</v>
-      </c>
       <c r="F27" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G27" s="3">
         <v>117</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="2">
+        <v>87560</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>238</v>
+        <v>47</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="D28">
         <v>813.7</v>
       </c>
-      <c r="E28" s="2">
-        <v>66006</v>
-      </c>
       <c r="F28" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G28" s="3">
         <v>32</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="2">
+        <v>66006</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>239</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="D29">
         <v>813.7</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="6">
+        <v>5945</v>
+      </c>
+      <c r="H29" s="2">
         <v>164104</v>
       </c>
-      <c r="F29" t="s">
-        <v>205</v>
-      </c>
-      <c r="G29" s="7">
-        <v>5945</v>
-      </c>
-      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>240</v>
+        <v>49</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="D30">
         <v>813.7</v>
       </c>
-      <c r="E30" s="2">
-        <v>43000</v>
-      </c>
       <c r="F30" t="s">
-        <v>205</v>
-      </c>
-      <c r="H30" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H30" s="2">
+        <v>134600</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>241</v>
+        <v>51</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="D31">
         <v>813.7</v>
       </c>
-      <c r="E31" s="2">
-        <v>112290</v>
-      </c>
       <c r="F31" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G31" s="3">
         <v>199</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="2">
+        <v>112290</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>242</v>
+        <v>53</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="D32">
         <v>813.7</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="2">
         <v>213382</v>
       </c>
-      <c r="F32" t="s">
-        <v>205</v>
-      </c>
-      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>243</v>
+        <v>55</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="D33">
         <v>813.7</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="6">
+        <v>1557</v>
+      </c>
+      <c r="H33" s="2">
         <v>140436</v>
       </c>
-      <c r="F33" t="s">
-        <v>205</v>
-      </c>
-      <c r="G33" s="7">
-        <v>1557</v>
-      </c>
-      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>244</v>
+        <v>57</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="D34">
         <v>813.7</v>
       </c>
-      <c r="E34" s="2">
-        <v>65532</v>
-      </c>
       <c r="F34" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G34" s="3">
         <v>382</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="2">
+        <v>65532</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>245</v>
+        <v>59</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="D35">
         <v>813.7</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="6">
+        <v>1678</v>
+      </c>
+      <c r="H35" s="2">
         <v>62678</v>
       </c>
-      <c r="F35" t="s">
-        <v>205</v>
-      </c>
-      <c r="G35" s="7">
-        <v>1678</v>
-      </c>
-      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>246</v>
+        <v>61</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="D36">
         <v>813.7</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" s="6">
+        <v>1914</v>
+      </c>
+      <c r="H36" s="2">
         <v>194564</v>
       </c>
-      <c r="F36" t="s">
-        <v>205</v>
-      </c>
-      <c r="G36" s="7">
-        <v>1914</v>
-      </c>
-      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>247</v>
+        <v>63</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="D37">
         <v>813.7</v>
       </c>
-      <c r="E37" s="2">
-        <v>171196</v>
-      </c>
       <c r="F37" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G37" s="3">
         <v>643</v>
       </c>
-      <c r="H37" s="4"/>
+      <c r="H37" s="2">
+        <v>171196</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>201</v>
+        <v>171</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="D38">
         <v>813.7</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="2">
         <v>90000</v>
       </c>
-      <c r="F38" t="s">
-        <v>205</v>
-      </c>
-      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>248</v>
+        <v>16</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="D39">
         <v>813.7</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" s="6">
+        <v>11028</v>
+      </c>
+      <c r="H39" s="2">
         <v>66052</v>
       </c>
-      <c r="F39" t="s">
-        <v>205</v>
-      </c>
-      <c r="G39" s="7">
-        <v>11028</v>
-      </c>
-      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>249</v>
+        <v>66</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="D40">
         <v>813.7</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F40" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40" s="2">
         <v>29000</v>
       </c>
-      <c r="F40" t="s">
-        <v>205</v>
-      </c>
-      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>250</v>
+        <v>68</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="D41">
         <v>813.7</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="6">
+        <v>27408</v>
+      </c>
+      <c r="H41" s="2">
         <v>105288</v>
       </c>
-      <c r="F41" t="s">
-        <v>205</v>
-      </c>
-      <c r="G41" s="7">
-        <v>27408</v>
-      </c>
-      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>251</v>
+        <v>70</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="D42">
         <v>813.7</v>
       </c>
-      <c r="E42" s="2">
+      <c r="F42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G42" s="6">
+        <v>5630</v>
+      </c>
+      <c r="H42" s="2">
         <v>130242</v>
       </c>
-      <c r="F42" t="s">
-        <v>205</v>
-      </c>
-      <c r="G42" s="7">
-        <v>5630</v>
-      </c>
-      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>252</v>
+        <v>63</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="D43">
         <v>813.7</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F43" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="6">
+        <v>8388</v>
+      </c>
+      <c r="H43" s="2">
         <v>51000</v>
       </c>
-      <c r="F43" t="s">
-        <v>205</v>
-      </c>
-      <c r="G43" s="7">
-        <v>8388</v>
-      </c>
-      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>253</v>
+        <v>73</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="D44">
         <v>813.7</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F44" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1843</v>
+      </c>
+      <c r="H44" s="2">
         <v>159330</v>
       </c>
-      <c r="F44" t="s">
-        <v>205</v>
-      </c>
-      <c r="G44" s="7">
-        <v>1843</v>
-      </c>
-      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>254</v>
+        <v>75</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="D45">
         <v>813.7</v>
       </c>
-      <c r="E45" s="2">
-        <v>41760</v>
-      </c>
       <c r="F45" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G45" s="3">
         <v>44</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="2">
+        <v>41760</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>255</v>
+        <v>76</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="D46">
         <v>813.7</v>
       </c>
-      <c r="E46" s="2">
-        <v>36000</v>
-      </c>
       <c r="F46" t="s">
-        <v>205</v>
-      </c>
-      <c r="G46" s="7">
+        <v>176</v>
+      </c>
+      <c r="G46" s="6">
         <v>28637</v>
       </c>
-      <c r="H46" s="4"/>
+      <c r="H46" s="2">
+        <v>106000</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>256</v>
+        <v>77</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="D47">
         <v>813.7</v>
       </c>
-      <c r="E47" s="2">
-        <v>27000</v>
-      </c>
       <c r="F47" t="s">
-        <v>205</v>
-      </c>
-      <c r="H47" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="H47" s="2">
+        <v>82600</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>257</v>
+        <v>79</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="D48">
         <v>813.7</v>
       </c>
-      <c r="E48" s="2">
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" s="6">
+        <v>10218</v>
+      </c>
+      <c r="H48" s="2">
         <v>425178</v>
       </c>
-      <c r="F48" t="s">
-        <v>205</v>
-      </c>
-      <c r="G48" s="7">
-        <v>10218</v>
-      </c>
-      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>258</v>
+        <v>80</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="D49">
         <v>813.7</v>
       </c>
-      <c r="E49" s="2">
+      <c r="F49" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1393</v>
+      </c>
+      <c r="H49" s="2">
         <v>68420</v>
       </c>
-      <c r="F49" t="s">
-        <v>205</v>
-      </c>
-      <c r="G49" s="7">
-        <v>1393</v>
-      </c>
-      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>259</v>
+        <v>82</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="D50">
         <v>813.7</v>
       </c>
-      <c r="E50" s="2">
+      <c r="F50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="6">
+        <v>8025</v>
+      </c>
+      <c r="H50" s="2">
         <v>106275</v>
       </c>
-      <c r="F50" t="s">
-        <v>205</v>
-      </c>
-      <c r="G50" s="7">
-        <v>8025</v>
-      </c>
-      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>260</v>
+        <v>84</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="D51">
         <v>813.7</v>
       </c>
-      <c r="E51" s="2">
-        <v>94686</v>
-      </c>
       <c r="F51" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G51" s="3">
         <v>926</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="2">
+        <v>94686</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>287</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>261</v>
+        <v>85</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="D52">
         <v>814.7</v>
       </c>
-      <c r="E52" s="2">
-        <v>15000</v>
-      </c>
       <c r="F52" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G52" s="3">
         <v>512</v>
       </c>
-      <c r="H52" s="4"/>
+      <c r="H52" s="2">
+        <v>33800</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>288</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>213</v>
+        <v>86</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="D53">
         <v>814.7</v>
       </c>
-      <c r="E53" s="2">
+      <c r="F53" t="s">
+        <v>168</v>
+      </c>
+      <c r="G53" s="6">
+        <v>5958</v>
+      </c>
+      <c r="H53" s="2">
         <v>160000</v>
       </c>
-      <c r="F53" t="s">
-        <v>196</v>
-      </c>
-      <c r="G53" s="7">
-        <v>5958</v>
-      </c>
-      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>262</v>
+        <v>88</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="D54">
         <v>814.7</v>
       </c>
-      <c r="E54" s="2">
+      <c r="F54" t="s">
+        <v>168</v>
+      </c>
+      <c r="G54" s="6">
+        <v>5393</v>
+      </c>
+      <c r="H54" s="2">
         <v>93273</v>
       </c>
-      <c r="F54" t="s">
-        <v>196</v>
-      </c>
-      <c r="G54" s="7">
-        <v>5393</v>
-      </c>
-      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>263</v>
+        <v>90</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="D55">
         <v>814.7</v>
       </c>
-      <c r="E55" s="2">
-        <v>89445</v>
-      </c>
       <c r="F55" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G55" s="3">
         <v>21</v>
       </c>
-      <c r="H55" s="4"/>
+      <c r="H55" s="2">
+        <v>89445</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>214</v>
+        <v>92</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="D56">
         <v>814.7</v>
       </c>
-      <c r="E56" s="2">
-        <v>76314</v>
-      </c>
       <c r="F56" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G56" s="3">
         <v>472</v>
       </c>
-      <c r="H56" s="4"/>
+      <c r="H56" s="2">
+        <v>76314</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>264</v>
+        <v>94</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="D57">
         <v>814.7</v>
       </c>
-      <c r="E57" s="2">
-        <v>13464</v>
-      </c>
       <c r="F57" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G57" s="3">
         <v>463</v>
       </c>
-      <c r="H57" s="4"/>
+      <c r="H57" s="2">
+        <v>13464</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>265</v>
+        <v>85</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="D58">
         <v>814.7</v>
       </c>
-      <c r="E58" s="2">
+      <c r="F58" t="s">
+        <v>168</v>
+      </c>
+      <c r="G58" s="6">
+        <v>6895</v>
+      </c>
+      <c r="H58" s="2">
         <v>85652</v>
       </c>
-      <c r="F58" t="s">
-        <v>196</v>
-      </c>
-      <c r="G58" s="7">
-        <v>6895</v>
-      </c>
-      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>289</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>266</v>
+        <v>96</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="D59">
         <v>814.7</v>
       </c>
-      <c r="E59" s="2">
-        <v>15000</v>
-      </c>
       <c r="F59" t="s">
-        <v>196</v>
-      </c>
-      <c r="G59" s="7">
+        <v>168</v>
+      </c>
+      <c r="G59" s="6">
         <v>10969</v>
       </c>
-      <c r="H59" s="4"/>
+      <c r="H59" s="2">
+        <v>130400</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>267</v>
+        <v>98</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="D60">
         <v>814.7</v>
       </c>
-      <c r="E60" s="2">
+      <c r="F60" t="s">
+        <v>168</v>
+      </c>
+      <c r="G60" s="6">
+        <v>6200</v>
+      </c>
+      <c r="H60" s="2">
         <v>22338</v>
       </c>
-      <c r="F60" t="s">
-        <v>196</v>
-      </c>
-      <c r="G60" s="7">
-        <v>6200</v>
-      </c>
-      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>268</v>
+        <v>100</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="D61">
         <v>814.7</v>
       </c>
-      <c r="E61" s="2">
+      <c r="F61" t="s">
+        <v>168</v>
+      </c>
+      <c r="G61" s="6">
+        <v>9373</v>
+      </c>
+      <c r="H61" s="2">
         <v>121158</v>
       </c>
-      <c r="F61" t="s">
-        <v>196</v>
-      </c>
-      <c r="G61" s="7">
-        <v>9373</v>
-      </c>
-      <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>269</v>
+        <v>102</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="D62">
         <v>814.7</v>
       </c>
-      <c r="E62" s="2">
-        <v>112175</v>
-      </c>
       <c r="F62" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G62" s="3">
         <v>25</v>
       </c>
-      <c r="H62" s="4"/>
+      <c r="H62" s="2">
+        <v>112175</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>270</v>
+        <v>104</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="D63">
         <v>814.7</v>
       </c>
-      <c r="E63" s="2">
-        <v>107060</v>
-      </c>
       <c r="F63" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G63" s="3">
         <v>202</v>
       </c>
-      <c r="H63" s="4"/>
+      <c r="H63" s="2">
+        <v>107060</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>275</v>
+        <v>106</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="D64">
         <v>814.7</v>
       </c>
-      <c r="E64" s="2">
+      <c r="F64" t="s">
+        <v>168</v>
+      </c>
+      <c r="G64" s="6">
+        <v>2576</v>
+      </c>
+      <c r="H64" s="2">
         <v>65208</v>
       </c>
-      <c r="F64" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" s="7">
-        <v>2576</v>
-      </c>
-      <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>215</v>
+        <v>108</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="D65">
         <v>814.7</v>
       </c>
-      <c r="E65" s="2">
+      <c r="F65" t="s">
+        <v>168</v>
+      </c>
+      <c r="G65" s="6">
+        <v>7494</v>
+      </c>
+      <c r="H65" s="2">
         <v>148030</v>
       </c>
-      <c r="F65" t="s">
-        <v>196</v>
-      </c>
-      <c r="G65" s="7">
-        <v>7494</v>
-      </c>
-      <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>271</v>
+        <v>110</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="D66">
         <v>814.7</v>
       </c>
-      <c r="E66" s="2">
+      <c r="F66" t="s">
+        <v>168</v>
+      </c>
+      <c r="G66" s="6">
+        <v>6404</v>
+      </c>
+      <c r="H66" s="2">
         <v>147168</v>
       </c>
-      <c r="F66" t="s">
-        <v>196</v>
-      </c>
-      <c r="G66" s="7">
-        <v>6404</v>
-      </c>
-      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>276</v>
+        <v>112</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="D67">
         <v>814.7</v>
       </c>
-      <c r="E67" s="2">
+      <c r="F67" t="s">
+        <v>168</v>
+      </c>
+      <c r="G67" s="6">
+        <v>3498</v>
+      </c>
+      <c r="H67" s="2">
         <v>74095</v>
       </c>
-      <c r="F67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67" s="7">
-        <v>3498</v>
-      </c>
-      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>272</v>
+        <v>114</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="D68">
         <v>814.6</v>
       </c>
-      <c r="E68" s="2">
-        <v>100097</v>
-      </c>
       <c r="F68" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G68" s="3">
         <v>6</v>
       </c>
-      <c r="H68" s="4"/>
+      <c r="H68" s="2">
+        <v>100097</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>277</v>
+        <v>116</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="D69">
         <v>814.7</v>
       </c>
-      <c r="E69" s="2">
-        <v>82536</v>
-      </c>
       <c r="F69" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G69" s="3">
         <v>999</v>
       </c>
-      <c r="H69" s="4"/>
+      <c r="H69" s="2">
+        <v>82536</v>
+      </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>132</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>273</v>
+        <v>118</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="D70">
         <v>814.7</v>
       </c>
-      <c r="E70" s="2">
-        <v>60354</v>
-      </c>
       <c r="F70" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G70" s="3">
         <v>367</v>
       </c>
-      <c r="H70" s="4"/>
+      <c r="H70" s="2">
+        <v>60354</v>
+      </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>216</v>
+        <v>120</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="D71">
         <v>814.7</v>
       </c>
-      <c r="E71" s="2">
+      <c r="F71" t="s">
+        <v>168</v>
+      </c>
+      <c r="G71" s="6">
+        <v>11008</v>
+      </c>
+      <c r="H71" s="2">
         <v>84076</v>
       </c>
-      <c r="F71" t="s">
-        <v>196</v>
-      </c>
-      <c r="G71" s="7">
-        <v>11008</v>
-      </c>
-      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>274</v>
+        <v>122</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="D72">
         <v>814.7</v>
       </c>
-      <c r="E72" s="2">
-        <v>78196</v>
-      </c>
       <c r="F72" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G72" s="3">
         <v>160</v>
       </c>
-      <c r="H72" s="4"/>
+      <c r="H72" s="2">
+        <v>78196</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>291</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>278</v>
+        <v>123</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="D73">
         <v>814.7</v>
       </c>
-      <c r="E73" s="2">
-        <v>51000</v>
-      </c>
       <c r="F73" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G73" s="3">
         <v>17</v>
       </c>
-      <c r="H73" s="4"/>
+      <c r="H73" s="2">
+        <v>126400</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="B74" t="s">
-        <v>139</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>203</v>
+        <v>124</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="D74">
         <v>814.7</v>
       </c>
-      <c r="E74" s="2">
-        <v>75953</v>
-      </c>
       <c r="F74" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G74" s="3">
         <v>63</v>
       </c>
-      <c r="H74" s="4"/>
+      <c r="H74" s="2">
+        <v>75953</v>
+      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>279</v>
+        <v>126</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="D75">
         <v>814.7</v>
       </c>
-      <c r="E75" s="2">
+      <c r="F75" t="s">
+        <v>168</v>
+      </c>
+      <c r="G75" s="6">
+        <v>2012</v>
+      </c>
+      <c r="H75" s="2">
         <v>149499</v>
       </c>
-      <c r="F75" t="s">
-        <v>196</v>
-      </c>
-      <c r="G75" s="7">
-        <v>2012</v>
-      </c>
-      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>280</v>
+        <v>88</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="D76">
         <v>814.7</v>
       </c>
-      <c r="E76" s="2">
+      <c r="F76" t="s">
+        <v>168</v>
+      </c>
+      <c r="G76" s="6">
+        <v>13739</v>
+      </c>
+      <c r="H76" s="2">
         <v>51337</v>
       </c>
-      <c r="F76" t="s">
-        <v>196</v>
-      </c>
-      <c r="G76" s="7">
-        <v>13739</v>
-      </c>
-      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>281</v>
+        <v>128</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="D77">
         <v>814.7</v>
       </c>
-      <c r="E77" s="2">
-        <v>20000</v>
-      </c>
       <c r="F77" t="s">
-        <v>196</v>
-      </c>
-      <c r="H77" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="H77" s="2">
+        <v>52400</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>282</v>
+        <v>129</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="D78">
         <v>814.7</v>
       </c>
-      <c r="E78" s="2">
-        <v>34000</v>
-      </c>
       <c r="F78" t="s">
-        <v>196</v>
-      </c>
-      <c r="G78" s="7">
+        <v>168</v>
+      </c>
+      <c r="G78" s="6">
         <v>1254</v>
       </c>
-      <c r="H78" s="4"/>
+      <c r="H78" s="2">
+        <v>96000</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B79" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>283</v>
+        <v>131</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="D79">
         <v>814.7</v>
       </c>
-      <c r="E79" s="2">
+      <c r="F79" t="s">
+        <v>168</v>
+      </c>
+      <c r="G79" s="6">
+        <v>11476</v>
+      </c>
+      <c r="H79" s="2">
         <v>65583</v>
       </c>
-      <c r="F79" t="s">
-        <v>196</v>
-      </c>
-      <c r="G79" s="7">
-        <v>11476</v>
-      </c>
-      <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>293</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>284</v>
+        <v>132</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="D80">
         <v>814.7</v>
       </c>
-      <c r="E80" s="2">
-        <v>26000</v>
-      </c>
       <c r="F80" t="s">
-        <v>196</v>
-      </c>
-      <c r="H80" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="H80" s="2">
+        <v>73000</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>285</v>
+        <v>133</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="D81">
         <v>814.7</v>
       </c>
-      <c r="E81" s="2">
-        <v>18000</v>
-      </c>
       <c r="F81" t="s">
-        <v>196</v>
-      </c>
-      <c r="H81" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="H81" s="2">
+        <v>46200</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>153</v>
+        <v>295</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>286</v>
+        <v>134</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="D82">
         <v>814.7</v>
       </c>
-      <c r="E82">
-        <v>12000</v>
-      </c>
       <c r="F82" t="s">
-        <v>196</v>
-      </c>
-      <c r="H82" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="H82">
+        <v>28800</v>
+      </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>296</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>287</v>
+        <v>135</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="D83">
         <v>814.7</v>
       </c>
-      <c r="E83" s="2">
-        <v>28000</v>
-      </c>
       <c r="F83" t="s">
-        <v>196</v>
-      </c>
-      <c r="H83" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="H83" s="2">
+        <v>80000</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>157</v>
+        <v>297</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>217</v>
+        <v>136</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="D84">
         <v>814.7</v>
       </c>
-      <c r="E84">
-        <v>19000</v>
-      </c>
       <c r="F84" t="s">
-        <v>196</v>
-      </c>
-      <c r="G84" s="7">
+        <v>168</v>
+      </c>
+      <c r="G84" s="6">
         <v>4248</v>
       </c>
-      <c r="H84" s="4"/>
+      <c r="H84">
+        <v>49400</v>
+      </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>159</v>
+        <v>298</v>
       </c>
       <c r="B85" t="s">
-        <v>160</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>288</v>
+        <v>137</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="D85">
         <v>814.7</v>
       </c>
-      <c r="E85" s="2">
-        <v>27000</v>
-      </c>
       <c r="F85" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G85" s="3">
         <v>170</v>
       </c>
-      <c r="H85" s="4"/>
+      <c r="H85" s="2">
+        <v>79400</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>161</v>
+        <v>299</v>
       </c>
       <c r="B86" t="s">
-        <v>162</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>289</v>
+        <v>138</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="D86">
         <v>814.7</v>
       </c>
-      <c r="E86">
-        <v>34000</v>
-      </c>
       <c r="F86" t="s">
-        <v>196</v>
-      </c>
-      <c r="G86" s="7">
+        <v>168</v>
+      </c>
+      <c r="G86" s="6">
         <v>6820</v>
       </c>
-      <c r="H86" s="4"/>
+      <c r="H86">
+        <v>99800</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>163</v>
+        <v>300</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>290</v>
+        <v>139</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="D87">
         <v>814.7</v>
       </c>
-      <c r="E87" s="2">
-        <v>15000</v>
-      </c>
       <c r="F87" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G87" s="3">
         <v>8</v>
       </c>
-      <c r="H87" s="4"/>
+      <c r="H87" s="2">
+        <v>33000</v>
+      </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>291</v>
+        <v>141</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="D88">
         <v>814.7</v>
       </c>
-      <c r="E88" s="2">
-        <v>102624</v>
-      </c>
       <c r="F88" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G88" s="3">
         <v>309</v>
       </c>
-      <c r="H88" s="4"/>
+      <c r="H88" s="2">
+        <v>102624</v>
+      </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>292</v>
+        <v>143</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>263</v>
       </c>
       <c r="D89">
         <v>814.7</v>
       </c>
-      <c r="E89" s="2">
+      <c r="F89" t="s">
+        <v>168</v>
+      </c>
+      <c r="G89" s="6">
+        <v>1525</v>
+      </c>
+      <c r="H89" s="2">
         <v>81900</v>
       </c>
-      <c r="F89" t="s">
-        <v>196</v>
-      </c>
-      <c r="G89" s="7">
-        <v>1525</v>
-      </c>
-      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>301</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>293</v>
+        <v>144</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="D90">
         <v>814.7</v>
       </c>
-      <c r="E90" s="2">
-        <v>45000</v>
-      </c>
       <c r="F90" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="G90" s="3">
         <v>598</v>
       </c>
-      <c r="H90" s="4"/>
+      <c r="H90" s="2">
+        <v>45000</v>
+      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>294</v>
+        <v>145</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="D91">
         <v>814.7</v>
       </c>
-      <c r="E91" s="2">
-        <v>32000</v>
-      </c>
       <c r="F91" t="s">
-        <v>196</v>
-      </c>
-      <c r="G91" s="7">
+        <v>168</v>
+      </c>
+      <c r="G91" s="6">
         <v>2170</v>
       </c>
-      <c r="H91" s="4"/>
+      <c r="H91" s="2">
+        <v>86800</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>295</v>
+        <v>147</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="D92">
         <v>816.7</v>
       </c>
-      <c r="E92" s="2">
-        <v>38400</v>
-      </c>
       <c r="F92" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G92" s="3">
         <v>25</v>
       </c>
-      <c r="H92" s="4"/>
+      <c r="H92" s="2">
+        <v>38400</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>176</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>296</v>
+        <v>149</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="D93">
         <v>816.7</v>
       </c>
-      <c r="E93" s="2">
-        <v>141264</v>
-      </c>
       <c r="F93" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G93" s="3">
         <v>726</v>
       </c>
-      <c r="H93" s="4"/>
+      <c r="H93" s="2">
+        <v>141264</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>178</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>218</v>
+        <v>151</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="D94">
         <v>816.6</v>
       </c>
-      <c r="E94" s="2">
-        <v>46060</v>
-      </c>
       <c r="F94" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G94" s="3">
         <v>162</v>
       </c>
-      <c r="H94" s="4"/>
+      <c r="H94" s="2">
+        <v>46060</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>297</v>
+        <v>153</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="D95">
         <v>816.6</v>
       </c>
-      <c r="E95" s="2">
-        <v>95948</v>
-      </c>
       <c r="F95" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G95" s="3">
         <v>314</v>
       </c>
-      <c r="H95" s="4"/>
+      <c r="H95" s="2">
+        <v>95948</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>298</v>
+        <v>155</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>269</v>
       </c>
       <c r="D96">
         <v>816.7</v>
       </c>
-      <c r="E96">
+      <c r="F96" t="s">
+        <v>190</v>
+      </c>
+      <c r="H96">
         <v>3924</v>
       </c>
-      <c r="F96" t="s">
-        <v>219</v>
-      </c>
-      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="B97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>299</v>
+        <v>156</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="D97">
         <v>816.6</v>
       </c>
-      <c r="E97" s="2">
-        <v>177968</v>
-      </c>
       <c r="F97" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G97" s="3">
         <v>253</v>
       </c>
-      <c r="H97" s="4"/>
+      <c r="H97" s="2">
+        <v>177968</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>184</v>
+        <v>303</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>197</v>
+        <v>157</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="D98">
         <v>816.6</v>
       </c>
-      <c r="E98" s="2">
-        <v>52000</v>
-      </c>
       <c r="F98" t="s">
-        <v>219</v>
-      </c>
-      <c r="G98" s="7">
+        <v>190</v>
+      </c>
+      <c r="G98" s="6">
         <v>5169</v>
       </c>
-      <c r="H98" s="4"/>
+      <c r="H98" s="2">
+        <v>165600</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>187</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>300</v>
+        <v>159</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="D99">
         <v>816.7</v>
       </c>
-      <c r="E99" s="2">
-        <v>135136</v>
-      </c>
       <c r="F99" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="G99" s="3">
         <v>36</v>
       </c>
-      <c r="H99" s="4"/>
+      <c r="H99" s="2">
+        <v>135136</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="B100" t="s">
-        <v>189</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>301</v>
+        <v>161</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="D100">
         <v>816.7</v>
       </c>
-      <c r="E100" s="2">
+      <c r="F100" t="s">
+        <v>190</v>
+      </c>
+      <c r="H100" s="2">
         <v>126357</v>
       </c>
-      <c r="F100" t="s">
-        <v>219</v>
-      </c>
-      <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>302</v>
+        <v>163</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="D101">
         <v>816.7</v>
       </c>
-      <c r="E101" s="2">
+      <c r="F101" t="s">
+        <v>190</v>
+      </c>
+      <c r="G101" s="6">
+        <v>3280</v>
+      </c>
+      <c r="H101" s="2">
         <v>58320</v>
       </c>
-      <c r="F101" t="s">
-        <v>219</v>
-      </c>
-      <c r="G101" s="7">
-        <v>3280</v>
-      </c>
-      <c r="H101" s="4"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C104" s="1"/>
-      <c r="E104" s="2"/>
+      <c r="H104" s="2"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C105" s="1"/>
-      <c r="E105" s="2"/>
+      <c r="H105" s="2"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C106" s="1"/>
-      <c r="E106" s="2"/>
+      <c r="H106" s="2"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E107" s="2"/>
+      <c r="H107" s="2"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C108" s="1"/>
-      <c r="E108" s="2"/>
+      <c r="H108" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
